--- a/data/Conferences.xlsx
+++ b/data/Conferences.xlsx
@@ -1565,57 +1565,57 @@
       <c r="K15" s="60" t="inlineStr"/>
     </row>
     <row r="16" ht="28.5" customHeight="1" s="37">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>CCS</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>ACM Conference on Computer and Communications Security</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="40" t="inlineStr">
         <is>
           <t>Atlanta，USA</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>October, TBD</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>10.11-10.15</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H16" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/ccs/</t>
         </is>
       </c>
-      <c r="J16" s="67" t="inlineStr">
+      <c r="J16" s="44" t="inlineStr">
         <is>
           <t>https://www.sigsac.org/ccs/CCS2027/</t>
         </is>
       </c>
-      <c r="K16" s="69" t="inlineStr"/>
+      <c r="K16" s="58" t="inlineStr"/>
     </row>
     <row r="17" ht="42.75" customHeight="1" s="37">
       <c r="A17" s="13" t="inlineStr">
@@ -1671,57 +1671,57 @@
       <c r="K17" s="60" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>S&amp;P</t>
         </is>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>IEEE Symposium on Security and Privacy</t>
         </is>
       </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>MONTREAL, CANADA</t>
         </is>
       </c>
-      <c r="E18" s="41" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>05.17-05.19</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G18" s="40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H18" s="42" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I18" s="43" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/sp/</t>
         </is>
       </c>
-      <c r="J18" s="44" t="inlineStr">
+      <c r="J18" s="67" t="inlineStr">
         <is>
           <t>https://sp2027.ieee-security.org/index.html</t>
         </is>
       </c>
-      <c r="K18" s="58" t="inlineStr"/>
+      <c r="K18" s="69" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2450,57 +2450,57 @@
       <c r="K32" s="60" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>数据库</t>
         </is>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>SIGKDD</t>
         </is>
       </c>
-      <c r="C33" s="39" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>ACM SIGKDD Conference on Knowledge Discovery and Data Mining</t>
         </is>
       </c>
-      <c r="D33" s="40" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>San Jose, (California), USA</t>
         </is>
       </c>
-      <c r="E33" s="41" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>08.01-08.05</t>
         </is>
       </c>
-      <c r="F33" s="40" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G33" s="40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H33" s="42" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I33" s="43" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/kdd/</t>
         </is>
       </c>
-      <c r="J33" s="44" t="inlineStr">
+      <c r="J33" s="67" t="inlineStr">
         <is>
           <t>https://kdd2027.kdd.org/</t>
         </is>
       </c>
-      <c r="K33" s="56" t="inlineStr"/>
+      <c r="K33" s="60" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
@@ -2768,57 +2768,57 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="38" t="inlineStr">
         <is>
           <t>理论</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="38" t="inlineStr">
         <is>
           <t>CAV</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="39" t="inlineStr">
         <is>
           <t>International Conference on Computer Aided Verification</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>Amsterdam, Netherlands</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>7.19-7.23</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="D39" s="40" t="inlineStr">
+        <is>
+          <t>KIT, Amsterdam, The Netherlands</t>
+        </is>
+      </c>
+      <c r="E39" s="41" t="inlineStr">
+        <is>
+          <t>07.19-07.23</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="40" t="inlineStr">
         <is>
           <t>2026.09.15</t>
         </is>
       </c>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="H39" s="42" t="inlineStr">
         <is>
           <t>Springer</t>
         </is>
       </c>
-      <c r="I39" s="17" t="inlineStr">
+      <c r="I39" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/cav/</t>
         </is>
       </c>
-      <c r="J39" s="67" t="inlineStr">
+      <c r="J39" s="44" t="inlineStr">
         <is>
           <t>https://conferences.i-cav.org/2027/</t>
         </is>
       </c>
-      <c r="K39" s="70" t="inlineStr">
+      <c r="K39" s="59" t="inlineStr">
         <is>
           <t>https://conferences.i-cav.org/2027/</t>
         </is>
@@ -2984,57 +2984,61 @@
       </c>
     </row>
     <row r="43" ht="28.5" customHeight="1" s="37">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>多媒体</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>IEEE VIS</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="39" t="inlineStr">
         <is>
           <t>IEEE Visualization Conference</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="45" t="inlineStr">
         <is>
           <t>Chicago, USA</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="E43" s="41" t="inlineStr">
         <is>
           <t>11.7-11.12</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="F43" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>2026.06.25</t>
+        </is>
+      </c>
+      <c r="H43" s="42" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="I43" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/visualization/</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr">
+      <c r="J43" s="46" t="inlineStr">
         <is>
           <t>https://www.computer.org/communities/vgtc</t>
         </is>
       </c>
-      <c r="K43" s="60" t="inlineStr"/>
+      <c r="K43" s="59" t="inlineStr">
+        <is>
+          <t>https://vis4climate.ivia.ch/workshop</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
@@ -3090,57 +3094,57 @@
       <c r="K44" s="60" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>软工</t>
         </is>
       </c>
-      <c r="B45" s="38" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>ISSTA</t>
         </is>
       </c>
-      <c r="C45" s="39" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>International Symposium on Software Testing and Analysis</t>
         </is>
       </c>
-      <c r="D45" s="40" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="E45" s="41" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>09.07-09.10</t>
         </is>
       </c>
-      <c r="F45" s="40" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>亚太</t>
         </is>
       </c>
-      <c r="G45" s="40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H45" s="42" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I45" s="43" t="inlineStr">
+      <c r="I45" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/issta/</t>
         </is>
       </c>
-      <c r="J45" s="44" t="inlineStr">
+      <c r="J45" s="67" t="inlineStr">
         <is>
           <t>https://conf.researchr.org/home/issta-2027</t>
         </is>
       </c>
-      <c r="K45" s="56" t="inlineStr"/>
+      <c r="K45" s="60" t="inlineStr"/>
     </row>
     <row r="46" ht="27" customHeight="1" s="37">
       <c r="A46" s="13" t="inlineStr">
@@ -3302,57 +3306,57 @@
       <c r="K48" s="60" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="38" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>CVPR</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="39" t="inlineStr">
         <is>
           <t>IEEE/CVF Computer Vision and Pattern Recognition Conference</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>Seattle, USA</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>6.20-6.24</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>Seattle, WA, United States</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>06.20-06.24</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H49" s="42" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/cvpr/</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>https://www.thecvf.com/?p=137</t>
-        </is>
-      </c>
-      <c r="K49" s="60" t="inlineStr"/>
+      <c r="J49" s="44" t="inlineStr">
+        <is>
+          <t>https://cvpr.thecvf.com/Conferences/2027</t>
+        </is>
+      </c>
+      <c r="K49" s="56" t="inlineStr"/>
     </row>
     <row r="50" ht="28.5" customHeight="1" s="37">
       <c r="A50" s="13" t="inlineStr">
@@ -3761,7 +3765,7 @@
       </c>
       <c r="J57" s="44" t="inlineStr">
         <is>
-          <t>https://acmweb2027.org/</t>
+          <t>https://www2027.thewebconf.org/</t>
         </is>
       </c>
       <c r="K57" s="59" t="inlineStr">
@@ -4086,111 +4090,111 @@
       <c r="K63" s="65" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="52" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B64" s="52" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>MLsys</t>
         </is>
       </c>
-      <c r="C64" s="39" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Conference on Machine Learning and Systems</t>
         </is>
       </c>
-      <c r="D64" s="53" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Bellevue, (Washington), USA</t>
         </is>
       </c>
-      <c r="E64" s="53" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F64" s="53" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G64" s="73" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H64" s="39" t="inlineStr">
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>MLSys/PMLR</t>
         </is>
       </c>
-      <c r="I64" s="46" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>https://mlsys.org/</t>
         </is>
       </c>
-      <c r="J64" s="44" t="inlineStr">
+      <c r="J64" s="67" t="inlineStr">
         <is>
           <t>https://mlsys.org/</t>
         </is>
       </c>
-      <c r="K64" s="63" t="inlineStr"/>
+      <c r="K64" s="65" t="inlineStr"/>
     </row>
     <row r="65" ht="29" customHeight="1" s="37">
-      <c r="A65" s="52" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>网络</t>
         </is>
       </c>
-      <c r="B65" s="52" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>MobiSys</t>
         </is>
       </c>
-      <c r="C65" s="39" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>ACM International Conference on Mobile Systems,
 Applications, and Services</t>
         </is>
       </c>
-      <c r="D65" s="53" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Ho Chi Minh City, Vietnam Important Dates TPC Self Nomination TBA Abstract Registration TBA Paper Submission TBA Early Rejection Notification TBA Rebuttal Period TBA Final Decision Notification TBA Final Camera-ready Deadline TBA IoT Day TBA Rising Stars Forum TBA N</t>
         </is>
       </c>
-      <c r="E65" s="53" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>06.21-06.25</t>
         </is>
       </c>
-      <c r="F65" s="53" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>亚太</t>
         </is>
       </c>
-      <c r="G65" s="73" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H65" s="39" t="inlineStr">
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I65" s="46" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>http://dblp.uni-trier.de/db/conf/mobisys/</t>
         </is>
       </c>
-      <c r="J65" s="44" t="inlineStr">
+      <c r="J65" s="67" t="inlineStr">
         <is>
           <t>https://www.sigmobile.org/mobisys/2027/</t>
         </is>
       </c>
-      <c r="K65" s="63" t="inlineStr"/>
+      <c r="K65" s="65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5729,77 +5733,78 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId150"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
@@ -5821,7 +5826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9570,29 +9575,56 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="0" t="inlineStr">
         <is>
           <t>WWW</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D151" s="0" t="inlineStr">
         <is>
           <t>2027.02.16</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E151" s="0" t="inlineStr">
         <is>
           <t>2026-08-31 12:01 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>IEEE VIS</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026.06.25</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-09-07 10:55 UTC</t>
         </is>
       </c>
     </row>

--- a/data/Conferences.xlsx
+++ b/data/Conferences.xlsx
@@ -945,57 +945,61 @@
       </c>
     </row>
     <row r="4" ht="28.5" customHeight="1" s="37">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>数据库</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>ICDE</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>IEEE International Conference on Data Engineering</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>Copenhagen, Denmark</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>05.17-05.21</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>2026.11.01</t>
+        </is>
+      </c>
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/icde/</t>
         </is>
       </c>
-      <c r="J4" s="67" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t>https://icde2027.github.io/</t>
         </is>
       </c>
-      <c r="K4" s="60" t="inlineStr"/>
+      <c r="K4" s="59" t="inlineStr">
+        <is>
+          <t>https://icde2027.github.io/cf-workshop-proposals.html</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28.5" customHeight="1" s="37">
       <c r="A5" s="13" t="inlineStr">
@@ -1565,57 +1569,57 @@
       <c r="K15" s="60" t="inlineStr"/>
     </row>
     <row r="16" ht="28.5" customHeight="1" s="37">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>CCS</t>
         </is>
       </c>
-      <c r="C16" s="39" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>ACM Conference on Computer and Communications Security</t>
         </is>
       </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Atlanta，USA</t>
         </is>
       </c>
-      <c r="E16" s="41" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>10.11-10.15</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G16" s="41" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H16" s="42" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I16" s="43" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/ccs/</t>
         </is>
       </c>
-      <c r="J16" s="44" t="inlineStr">
+      <c r="J16" s="67" t="inlineStr">
         <is>
           <t>https://www.sigsac.org/ccs/CCS2027/</t>
         </is>
       </c>
-      <c r="K16" s="58" t="inlineStr"/>
+      <c r="K16" s="69" t="inlineStr"/>
     </row>
     <row r="17" ht="42.75" customHeight="1" s="37">
       <c r="A17" s="13" t="inlineStr">
@@ -2295,57 +2299,61 @@
       <c r="K29" s="60" t="inlineStr"/>
     </row>
     <row r="30" ht="29" customHeight="1" s="37">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>DAC</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
         <is>
           <t>Design Automation Conference</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>San Jose, USA</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>7.11-7.14</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>San Jose, (CA), USA</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>07.11-07.14</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>2027.04.15</t>
+        </is>
+      </c>
+      <c r="H30" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I30" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/dac/</t>
         </is>
       </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>https://dac.com/2026/events/dac-2027</t>
-        </is>
-      </c>
-      <c r="K30" s="60" t="inlineStr"/>
+      <c r="J30" s="44" t="inlineStr">
+        <is>
+          <t>https://dac.com/2027/authors/call-for-contributions</t>
+        </is>
+      </c>
+      <c r="K30" s="59" t="inlineStr">
+        <is>
+          <t>https://dac.com/2027/program/workshop-call-for-proposals</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -2662,53 +2670,57 @@
       <c r="K36" s="60" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>理论</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>STOC</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="39" t="inlineStr">
         <is>
           <t>ACM Symposium on the Theory of Computing</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="D37" s="40" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, USA</t>
+        </is>
+      </c>
+      <c r="E37" s="41" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>北美</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H37" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="I37" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/stoc/</t>
         </is>
       </c>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="60" t="inlineStr"/>
+      <c r="J37" s="44" t="inlineStr">
+        <is>
+          <t>https://acm-stoc.org/stoc2027/</t>
+        </is>
+      </c>
+      <c r="K37" s="56" t="inlineStr"/>
     </row>
     <row r="38" ht="28.5" customHeight="1" s="37">
       <c r="A38" s="13" t="inlineStr">
@@ -2768,57 +2780,57 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>理论</t>
         </is>
       </c>
-      <c r="B39" s="38" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>CAV</t>
         </is>
       </c>
-      <c r="C39" s="39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>International Conference on Computer Aided Verification</t>
         </is>
       </c>
-      <c r="D39" s="40" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>KIT, Amsterdam, The Netherlands</t>
         </is>
       </c>
-      <c r="E39" s="41" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>07.19-07.23</t>
         </is>
       </c>
-      <c r="F39" s="40" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G39" s="40" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>2026.09.15</t>
         </is>
       </c>
-      <c r="H39" s="42" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>Springer</t>
         </is>
       </c>
-      <c r="I39" s="43" t="inlineStr">
+      <c r="I39" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/cav/</t>
         </is>
       </c>
-      <c r="J39" s="44" t="inlineStr">
+      <c r="J39" s="67" t="inlineStr">
         <is>
           <t>https://conferences.i-cav.org/2027/</t>
         </is>
       </c>
-      <c r="K39" s="59" t="inlineStr">
+      <c r="K39" s="70" t="inlineStr">
         <is>
           <t>https://conferences.i-cav.org/2027/</t>
         </is>
@@ -2984,57 +2996,57 @@
       </c>
     </row>
     <row r="43" ht="28.5" customHeight="1" s="37">
-      <c r="A43" s="38" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>多媒体</t>
         </is>
       </c>
-      <c r="B43" s="38" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>IEEE VIS</t>
         </is>
       </c>
-      <c r="C43" s="39" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>IEEE Visualization Conference</t>
         </is>
       </c>
-      <c r="D43" s="45" t="inlineStr">
+      <c r="D43" s="18" t="inlineStr">
         <is>
           <t>Chicago, USA</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>11.7-11.12</t>
         </is>
       </c>
-      <c r="F43" s="40" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G43" s="40" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>2026.06.25</t>
         </is>
       </c>
-      <c r="H43" s="42" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I43" s="43" t="inlineStr">
+      <c r="I43" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/visualization/</t>
         </is>
       </c>
-      <c r="J43" s="46" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>https://www.computer.org/communities/vgtc</t>
         </is>
       </c>
-      <c r="K43" s="59" t="inlineStr">
+      <c r="K43" s="70" t="inlineStr">
         <is>
           <t>https://vis4climate.ivia.ch/workshop</t>
         </is>
@@ -3306,57 +3318,57 @@
       <c r="K48" s="60" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B49" s="38" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>CVPR</t>
         </is>
       </c>
-      <c r="C49" s="39" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>IEEE/CVF Computer Vision and Pattern Recognition Conference</t>
         </is>
       </c>
-      <c r="D49" s="40" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Seattle, WA, United States</t>
         </is>
       </c>
-      <c r="E49" s="41" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>06.20-06.24</t>
         </is>
       </c>
-      <c r="F49" s="40" t="inlineStr">
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G49" s="40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H49" s="42" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I49" s="43" t="inlineStr">
+      <c r="I49" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/cvpr/</t>
         </is>
       </c>
-      <c r="J49" s="44" t="inlineStr">
+      <c r="J49" s="67" t="inlineStr">
         <is>
           <t>https://cvpr.thecvf.com/Conferences/2027</t>
         </is>
       </c>
-      <c r="K49" s="56" t="inlineStr"/>
+      <c r="K49" s="60" t="inlineStr"/>
     </row>
     <row r="50" ht="28.5" customHeight="1" s="37">
       <c r="A50" s="13" t="inlineStr">
@@ -3718,57 +3730,57 @@
       <c r="K56" s="60" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="38" t="inlineStr">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="B57" s="38" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>WWW</t>
         </is>
       </c>
-      <c r="C57" s="39" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>International World Wide Web Conference</t>
         </is>
       </c>
-      <c r="D57" s="45" t="inlineStr">
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>Dublin, Ireland</t>
         </is>
       </c>
-      <c r="E57" s="50" t="inlineStr">
+      <c r="E57" s="27" t="inlineStr">
         <is>
           <t>05.10-05.14</t>
         </is>
       </c>
-      <c r="F57" s="45" t="inlineStr">
+      <c r="F57" s="18" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G57" s="45" t="inlineStr">
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>2027.02.16</t>
         </is>
       </c>
-      <c r="H57" s="42" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I57" s="43" t="inlineStr">
+      <c r="I57" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/www/</t>
         </is>
       </c>
-      <c r="J57" s="44" t="inlineStr">
+      <c r="J57" s="67" t="inlineStr">
         <is>
           <t>https://www2027.thewebconf.org/</t>
         </is>
       </c>
-      <c r="K57" s="59" t="inlineStr">
+      <c r="K57" s="70" t="inlineStr">
         <is>
           <t>https://www2027.thewebconf.org/workshops/</t>
         </is>
@@ -4250,57 +4262,61 @@
       <c r="K66" s="65" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="52" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="52" t="inlineStr">
         <is>
           <t>ICLR</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="39" t="inlineStr">
         <is>
           <t>International Conference on Learning Representations</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="53" t="inlineStr">
         <is>
           <t>San Francisco, (CA), USA</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="53" t="inlineStr">
         <is>
           <t>04.26-04.30</t>
         </is>
       </c>
-      <c r="F67" s="14" t="inlineStr">
+      <c r="F67" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G67" s="0" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="G67" s="73" t="inlineStr">
+        <is>
+          <t>2026.10.09</t>
+        </is>
+      </c>
+      <c r="H67" s="39" t="inlineStr">
         <is>
           <t>OpenReview</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I67" s="46" t="inlineStr">
         <is>
           <t>https://dblp.uni-trier.de/db/conf/iclr/index.html</t>
         </is>
       </c>
-      <c r="J67" s="67" t="inlineStr">
+      <c r="J67" s="44" t="inlineStr">
         <is>
           <t>https://iclr.cc/Conferences/2027</t>
         </is>
       </c>
-      <c r="K67" s="65" t="inlineStr"/>
+      <c r="K67" s="64" t="inlineStr">
+        <is>
+          <t>https://iclr.cc/Conferences/2027/CallForWorkshops</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5662,149 +5678,153 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId154"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
@@ -5826,7 +5846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9602,29 +9622,110 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="0" t="inlineStr">
         <is>
           <t>IEEE VIS</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D152" s="0" t="inlineStr">
         <is>
           <t>2026.06.25</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E152" s="0" t="inlineStr">
         <is>
           <t>2026-09-07 10:55 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ICDE</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026.11.01</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DAC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2027.04.15</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ICLR</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026.10.09</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:07 UTC</t>
         </is>
       </c>
     </row>

--- a/data/Conferences.xlsx
+++ b/data/Conferences.xlsx
@@ -243,7 +243,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -453,6 +453,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -945,57 +948,57 @@
       </c>
     </row>
     <row r="4" ht="28.5" customHeight="1" s="37">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>数据库</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ICDE</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>IEEE International Conference on Data Engineering</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Copenhagen, Denmark</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>05.17-05.21</t>
         </is>
       </c>
-      <c r="F4" s="40" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G4" s="40" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>2026.11.01</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/icde/</t>
         </is>
       </c>
-      <c r="J4" s="44" t="inlineStr">
+      <c r="J4" s="67" t="inlineStr">
         <is>
           <t>https://icde2027.github.io/</t>
         </is>
       </c>
-      <c r="K4" s="59" t="inlineStr">
+      <c r="K4" s="70" t="inlineStr">
         <is>
           <t>https://icde2027.github.io/cf-workshop-proposals.html</t>
         </is>
@@ -1153,57 +1156,61 @@
       <c r="K7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="27" customHeight="1" s="37">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>ASPLOS</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>International Conference on Architectural Support for Programming Languages and Operating Systems</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>Crete, Greece</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>04.11-04.15</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>2026.11.04</t>
+        </is>
+      </c>
+      <c r="H8" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/asplos/</t>
         </is>
       </c>
-      <c r="J8" s="67" t="inlineStr">
+      <c r="J8" s="44" t="inlineStr">
         <is>
           <t>https://www.asplos-conference.org/asplos2027/cfp/</t>
         </is>
       </c>
-      <c r="K8" s="60" t="inlineStr"/>
+      <c r="K8" s="59" t="inlineStr">
+        <is>
+          <t>https://www.asplos-conference.org/call-for-workshops-and-tutorials/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2091,53 +2098,57 @@
       <c r="K25" s="60" t="inlineStr"/>
     </row>
     <row r="26" ht="27" customHeight="1" s="37">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>软工</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>OOPSLA</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="39" t="inlineStr">
         <is>
           <t>Conference on Object-Oriented Programming Systems, Languages, and Applications</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="D26" s="40" t="inlineStr">
+        <is>
+          <t>Prague, Czechia</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>10.10-10.15</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H26" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I26" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/oopsla/</t>
         </is>
       </c>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="60" t="inlineStr"/>
+      <c r="J26" s="44" t="inlineStr">
+        <is>
+          <t>https://2027.splashcon.org/track/splashoopsla2027</t>
+        </is>
+      </c>
+      <c r="K26" s="56" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -2299,57 +2310,57 @@
       <c r="K29" s="60" t="inlineStr"/>
     </row>
     <row r="30" ht="29" customHeight="1" s="37">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>DAC</t>
         </is>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Design Automation Conference</t>
         </is>
       </c>
-      <c r="D30" s="40" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>San Jose, (CA), USA</t>
         </is>
       </c>
-      <c r="E30" s="41" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>07.11-07.14</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G30" s="40" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>2027.04.15</t>
         </is>
       </c>
-      <c r="H30" s="42" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I30" s="43" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/dac/</t>
         </is>
       </c>
-      <c r="J30" s="44" t="inlineStr">
+      <c r="J30" s="67" t="inlineStr">
         <is>
           <t>https://dac.com/2027/authors/call-for-contributions</t>
         </is>
       </c>
-      <c r="K30" s="59" t="inlineStr">
+      <c r="K30" s="70" t="inlineStr">
         <is>
           <t>https://dac.com/2027/program/workshop-call-for-proposals</t>
         </is>
@@ -2687,12 +2698,12 @@
       </c>
       <c r="D37" s="40" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, USA</t>
+          <t>Atlanta, (Georgia), USA</t>
         </is>
       </c>
       <c r="E37" s="41" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>06.06-06.11</t>
         </is>
       </c>
       <c r="F37" s="40" t="inlineStr">
@@ -2702,7 +2713,7 @@
       </c>
       <c r="G37" s="40" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2027.04.01</t>
         </is>
       </c>
       <c r="H37" s="42" t="inlineStr">
@@ -2720,7 +2731,11 @@
           <t>https://acm-stoc.org/stoc2027/</t>
         </is>
       </c>
-      <c r="K37" s="56" t="inlineStr"/>
+      <c r="K37" s="59" t="inlineStr">
+        <is>
+          <t>https://acm-stoc.org/stoc2027/</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="28.5" customHeight="1" s="37">
       <c r="A38" s="13" t="inlineStr">
@@ -3371,57 +3386,61 @@
       <c r="K49" s="60" t="inlineStr"/>
     </row>
     <row r="50" ht="28.5" customHeight="1" s="37">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="A50" s="38" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t>ICCV</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="39" t="inlineStr">
         <is>
           <t>International Conference on Computer Vision</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>10.2-10.8</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>Hong Kong, CN October</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr">
+        <is>
+          <t>10.02-10.08</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
         <is>
           <t>亚太</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H50" s="16" t="inlineStr">
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H50" s="42" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I50" s="17" t="inlineStr">
+      <c r="I50" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/iccv/</t>
         </is>
       </c>
-      <c r="J50" s="25" t="inlineStr">
-        <is>
-          <t>Upcoming CVF Sponsored Conferences – The Computer Vision Foundation</t>
-        </is>
-      </c>
-      <c r="K50" s="60" t="inlineStr"/>
+      <c r="J50" s="74" t="inlineStr">
+        <is>
+          <t>https://iccv.thecvf.com/Conferences/2027</t>
+        </is>
+      </c>
+      <c r="K50" s="59" t="inlineStr">
+        <is>
+          <t>https://iccv.thecvf.com/Conferences/2025/CallForWorkshops</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
@@ -3575,57 +3594,57 @@
       <c r="K53" s="60" t="inlineStr"/>
     </row>
     <row r="54" ht="42.75" customHeight="1" s="37">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="A54" s="38" t="inlineStr">
         <is>
           <t>多媒体</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t>SIGGRAPH</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="39" t="inlineStr">
         <is>
           <t>ACM Special Interest Group on Computer Graphics</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
-        <is>
-          <t>Anaheim, USA</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
+      <c r="D54" s="40" t="inlineStr">
+        <is>
+          <t>Anaheim, (California), USA</t>
+        </is>
+      </c>
+      <c r="E54" s="41" t="inlineStr">
         <is>
           <t>08.08-08.12</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F54" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
+      <c r="G54" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H54" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I54" s="17" t="inlineStr">
+      <c r="I54" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/siggraph/</t>
         </is>
       </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>https://blog.siggraph.org/2025/01/inspiration-innovation-and-ice-cream-kristy-pron-to-lead-siggraph-2027.html/</t>
-        </is>
-      </c>
-      <c r="K54" s="60" t="inlineStr"/>
+      <c r="J54" s="44" t="inlineStr">
+        <is>
+          <t>https://s2027.siggraph.org/</t>
+        </is>
+      </c>
+      <c r="K54" s="56" t="inlineStr"/>
     </row>
     <row r="55" ht="28.5" customHeight="1" s="37">
       <c r="A55" s="13" t="inlineStr">
@@ -4102,111 +4121,111 @@
       <c r="K63" s="65" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="52" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="52" t="inlineStr">
         <is>
           <t>MLsys</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="39" t="inlineStr">
         <is>
           <t>Conference on Machine Learning and Systems</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="53" t="inlineStr">
         <is>
           <t>Bellevue, (Washington), USA</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="E64" s="53" t="inlineStr">
+        <is>
+          <t>06.21-06.25</t>
+        </is>
+      </c>
+      <c r="F64" s="53" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G64" s="0" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="G64" s="73" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H64" s="39" t="inlineStr">
         <is>
           <t>MLSys/PMLR</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I64" s="46" t="inlineStr">
         <is>
           <t>https://mlsys.org/</t>
         </is>
       </c>
-      <c r="J64" s="67" t="inlineStr">
+      <c r="J64" s="44" t="inlineStr">
         <is>
           <t>https://mlsys.org/</t>
         </is>
       </c>
-      <c r="K64" s="65" t="inlineStr"/>
+      <c r="K64" s="63" t="inlineStr"/>
     </row>
     <row r="65" ht="29" customHeight="1" s="37">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="52" t="inlineStr">
         <is>
           <t>网络</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="52" t="inlineStr">
         <is>
           <t>MobiSys</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="39" t="inlineStr">
         <is>
           <t>ACM International Conference on Mobile Systems,
 Applications, and Services</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City, Vietnam Important Dates TPC Self Nomination TBA Abstract Registration TBA Paper Submission TBA Early Rejection Notification TBA Rebuttal Period TBA Final Decision Notification TBA Final Camera-ready Deadline TBA IoT Day TBA Rising Stars Forum TBA N</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="D65" s="53" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City, Vietnam Important Dates TPC Self-Nomination Deadline October</t>
+        </is>
+      </c>
+      <c r="E65" s="53" t="inlineStr">
         <is>
           <t>06.21-06.25</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F65" s="53" t="inlineStr">
         <is>
           <t>亚太</t>
         </is>
       </c>
-      <c r="G65" s="0" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="G65" s="73" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H65" s="39" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I65" s="46" t="inlineStr">
         <is>
           <t>http://dblp.uni-trier.de/db/conf/mobisys/</t>
         </is>
       </c>
-      <c r="J65" s="67" t="inlineStr">
+      <c r="J65" s="44" t="inlineStr">
         <is>
           <t>https://www.sigmobile.org/mobisys/2027/</t>
         </is>
       </c>
-      <c r="K65" s="65" t="inlineStr"/>
+      <c r="K65" s="63" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4262,57 +4281,57 @@
       <c r="K66" s="65" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="52" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B67" s="52" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>ICLR</t>
         </is>
       </c>
-      <c r="C67" s="39" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>International Conference on Learning Representations</t>
         </is>
       </c>
-      <c r="D67" s="53" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>San Francisco, (CA), USA</t>
         </is>
       </c>
-      <c r="E67" s="53" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>04.26-04.30</t>
         </is>
       </c>
-      <c r="F67" s="40" t="inlineStr">
+      <c r="F67" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G67" s="73" t="inlineStr">
+      <c r="G67" s="0" t="inlineStr">
         <is>
           <t>2026.10.09</t>
         </is>
       </c>
-      <c r="H67" s="39" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>OpenReview</t>
         </is>
       </c>
-      <c r="I67" s="46" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>https://dblp.uni-trier.de/db/conf/iclr/index.html</t>
         </is>
       </c>
-      <c r="J67" s="44" t="inlineStr">
+      <c r="J67" s="67" t="inlineStr">
         <is>
           <t>https://iclr.cc/Conferences/2027</t>
         </is>
       </c>
-      <c r="K67" s="64" t="inlineStr">
+      <c r="K67" s="72" t="inlineStr">
         <is>
           <t>https://iclr.cc/Conferences/2027/CallForWorkshops</t>
         </is>
@@ -4637,61 +4656,57 @@
       <c r="K73" s="65" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="52" t="inlineStr">
         <is>
           <t>机器人</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="52" t="inlineStr">
         <is>
           <t>RSS</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="39" t="inlineStr">
         <is>
           <t>Robotics: Science and Systems</t>
         </is>
       </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>Athens, Greece</t>
-        </is>
-      </c>
-      <c r="E74" s="14" t="inlineStr">
+      <c r="D74" s="40" t="inlineStr">
+        <is>
+          <t>Athens, Greece. Venue</t>
+        </is>
+      </c>
+      <c r="E74" s="40" t="inlineStr">
         <is>
           <t>07.06-07.11</t>
         </is>
       </c>
-      <c r="F74" s="14" t="inlineStr">
+      <c r="F74" s="40" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G74" s="0" t="inlineStr">
-        <is>
-          <t>2026.04.23</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="G74" s="73" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H74" s="39" t="inlineStr">
         <is>
           <t>RSS Foundation</t>
         </is>
       </c>
-      <c r="I74" s="29" t="inlineStr">
+      <c r="I74" s="55" t="inlineStr">
         <is>
           <t>https://roboticsconference.org/</t>
         </is>
       </c>
-      <c r="J74" s="6" t="inlineStr">
+      <c r="J74" s="46" t="inlineStr">
         <is>
           <t>https://roboticsconference.org/</t>
         </is>
       </c>
-      <c r="K74" s="72" t="inlineStr">
-        <is>
-          <t>https://roboticsconference.org/information/cfw/</t>
-        </is>
-      </c>
+      <c r="K74" s="63" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4853,57 +4868,57 @@
       <c r="K77" s="65" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="52" t="inlineStr">
         <is>
           <t>网络</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="52" t="inlineStr">
         <is>
           <t>WCNC</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="39" t="inlineStr">
         <is>
           <t>IEEE Wireless Communications and Networking Conference</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="53" t="inlineStr">
         <is>
           <t>Panama City, Panama</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E78" s="53" t="inlineStr">
         <is>
           <t>04.05-04.08</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F78" s="53" t="inlineStr">
         <is>
           <t>拉美</t>
         </is>
       </c>
-      <c r="G78" s="0" t="inlineStr">
-        <is>
-          <t>2026.10.01</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="G78" s="73" t="inlineStr">
+        <is>
+          <t>2026.10.05</t>
+        </is>
+      </c>
+      <c r="H78" s="39" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I78" s="46" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/wcnc/</t>
         </is>
       </c>
-      <c r="J78" s="67" t="inlineStr">
+      <c r="J78" s="44" t="inlineStr">
         <is>
           <t>https://wcnc2027.ieee-wcnc.org/</t>
         </is>
       </c>
-      <c r="K78" s="72" t="inlineStr">
+      <c r="K78" s="64" t="inlineStr">
         <is>
           <t>https://wcnc2027.ieee-wcnc.org/</t>
         </is>
@@ -5685,146 +5700,149 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId157"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
@@ -5846,7 +5864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9649,83 +9667,191 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="0" t="inlineStr">
         <is>
           <t>ICDE</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D153" s="0" t="inlineStr">
         <is>
           <t>2026.11.01</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E153" s="0" t="inlineStr">
         <is>
           <t>2026-09-14 11:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="0" t="inlineStr">
         <is>
           <t>DAC</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
         <is>
           <t>2027.04.15</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E154" s="0" t="inlineStr">
         <is>
           <t>2026-09-14 11:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="0" t="inlineStr">
         <is>
           <t>ICLR</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
         <is>
           <t>2026.10.09</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E155" s="0" t="inlineStr">
         <is>
           <t>2026-09-14 11:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ASPLOS</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026.11.04</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:17 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>STOC</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2027.04.01</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:17 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026.04.23</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:17 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>WCNC</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026.10.01</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026.10.05</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:17 UTC</t>
         </is>
       </c>
     </row>

--- a/data/Conferences.xlsx
+++ b/data/Conferences.xlsx
@@ -1156,110 +1156,114 @@
       <c r="K7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="27" customHeight="1" s="37">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>ASPLOS</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>International Conference on Architectural Support for Programming Languages and Operating Systems</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Crete, Greece</t>
         </is>
       </c>
-      <c r="E8" s="41" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>04.11-04.15</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G8" s="40" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>2026.11.04</t>
         </is>
       </c>
-      <c r="H8" s="42" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I8" s="43" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/asplos/</t>
         </is>
       </c>
-      <c r="J8" s="44" t="inlineStr">
+      <c r="J8" s="67" t="inlineStr">
         <is>
           <t>https://www.asplos-conference.org/asplos2027/cfp/</t>
         </is>
       </c>
-      <c r="K8" s="59" t="inlineStr">
+      <c r="K8" s="70" t="inlineStr">
         <is>
           <t>https://www.asplos-conference.org/call-for-workshops-and-tutorials/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>ISCA</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>International Symposium on Computer Architecture</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>Atlanta, (Georgia), USA</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>北美</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H9" s="42" t="inlineStr">
         <is>
           <t>ACM /IEEE</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/isca/</t>
         </is>
       </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="60" t="inlineStr"/>
+      <c r="J9" s="44" t="inlineStr">
+        <is>
+          <t>https://www.iscaconf.org/</t>
+        </is>
+      </c>
+      <c r="K9" s="56" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -1311,57 +1315,57 @@
       <c r="K10" s="60" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>EuroSys</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>ACM SIGOPS Annual Technical Conference</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>Rabat, Morocco</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>04.19-04.24</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>04.19-04.23</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>非洲</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H11" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="46" t="inlineStr">
         <is>
           <t>https://dblp.uni-trier.de/db/conf/usenix/index.html</t>
         </is>
       </c>
-      <c r="J11" s="67" t="inlineStr">
+      <c r="J11" s="44" t="inlineStr">
         <is>
           <t>https://2027.eurosys.org/</t>
         </is>
       </c>
-      <c r="K11" s="60" t="inlineStr"/>
+      <c r="K11" s="56" t="inlineStr"/>
     </row>
     <row r="12" ht="27" customHeight="1" s="37">
       <c r="A12" s="13" t="inlineStr">
@@ -1576,57 +1580,57 @@
       <c r="K15" s="60" t="inlineStr"/>
     </row>
     <row r="16" ht="28.5" customHeight="1" s="37">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>CCS</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>ACM Conference on Computer and Communications Security</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Atlanta，USA</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>Atlanta, USA</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
         <is>
           <t>10.11-10.15</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H16" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/ccs/</t>
         </is>
       </c>
-      <c r="J16" s="67" t="inlineStr">
+      <c r="J16" s="44" t="inlineStr">
         <is>
           <t>https://www.sigsac.org/ccs/CCS2027/</t>
         </is>
       </c>
-      <c r="K16" s="69" t="inlineStr"/>
+      <c r="K16" s="58" t="inlineStr"/>
     </row>
     <row r="17" ht="42.75" customHeight="1" s="37">
       <c r="A17" s="13" t="inlineStr">
@@ -2098,57 +2102,57 @@
       <c r="K25" s="60" t="inlineStr"/>
     </row>
     <row r="26" ht="27" customHeight="1" s="37">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>软工</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>OOPSLA</t>
         </is>
       </c>
-      <c r="C26" s="39" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Conference on Object-Oriented Programming Systems, Languages, and Applications</t>
         </is>
       </c>
-      <c r="D26" s="40" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Prague, Czechia</t>
         </is>
       </c>
-      <c r="E26" s="41" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>10.10-10.15</t>
         </is>
       </c>
-      <c r="F26" s="40" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G26" s="40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H26" s="42" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I26" s="43" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/oopsla/</t>
         </is>
       </c>
-      <c r="J26" s="44" t="inlineStr">
+      <c r="J26" s="67" t="inlineStr">
         <is>
           <t>https://2027.splashcon.org/track/splashoopsla2027</t>
         </is>
       </c>
-      <c r="K26" s="56" t="inlineStr"/>
+      <c r="K26" s="60" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -2367,53 +2371,57 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>软工</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>FM</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="39" t="inlineStr">
         <is>
           <t>International Symposium on Formal Methods</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>Athens, Greece</t>
+        </is>
+      </c>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>10.18-10.22</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H31" s="42" t="inlineStr">
         <is>
           <t>FME</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I31" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/fm/</t>
         </is>
       </c>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="60" t="inlineStr"/>
+      <c r="J31" s="44" t="inlineStr">
+        <is>
+          <t>https://www.fmeurope.org/feature/upcoming_conferences/</t>
+        </is>
+      </c>
+      <c r="K31" s="56" t="inlineStr"/>
     </row>
     <row r="32" ht="28.5" customHeight="1" s="37">
       <c r="A32" s="13" t="inlineStr">
@@ -2681,57 +2689,57 @@
       <c r="K36" s="60" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="38" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>理论</t>
         </is>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>STOC</t>
         </is>
       </c>
-      <c r="C37" s="39" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>ACM Symposium on the Theory of Computing</t>
         </is>
       </c>
-      <c r="D37" s="40" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>Atlanta, (Georgia), USA</t>
         </is>
       </c>
-      <c r="E37" s="41" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>06.06-06.11</t>
         </is>
       </c>
-      <c r="F37" s="40" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G37" s="40" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>2027.04.01</t>
         </is>
       </c>
-      <c r="H37" s="42" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I37" s="43" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/stoc/</t>
         </is>
       </c>
-      <c r="J37" s="44" t="inlineStr">
+      <c r="J37" s="67" t="inlineStr">
         <is>
           <t>https://acm-stoc.org/stoc2027/</t>
         </is>
       </c>
-      <c r="K37" s="59" t="inlineStr">
+      <c r="K37" s="70" t="inlineStr">
         <is>
           <t>https://acm-stoc.org/stoc2027/</t>
         </is>
@@ -2795,61 +2803,57 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="38" t="inlineStr">
         <is>
           <t>理论</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="38" t="inlineStr">
         <is>
           <t>CAV</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="39" t="inlineStr">
         <is>
           <t>International Conference on Computer Aided Verification</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="40" t="inlineStr">
         <is>
           <t>KIT, Amsterdam, The Netherlands</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="41" t="inlineStr">
         <is>
           <t>07.19-07.23</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>欧洲</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>2026.09.15</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H39" s="42" t="inlineStr">
         <is>
           <t>Springer</t>
         </is>
       </c>
-      <c r="I39" s="17" t="inlineStr">
+      <c r="I39" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/cav/</t>
         </is>
       </c>
-      <c r="J39" s="67" t="inlineStr">
+      <c r="J39" s="44" t="inlineStr">
         <is>
           <t>https://conferences.i-cav.org/2027/</t>
         </is>
       </c>
-      <c r="K39" s="70" t="inlineStr">
-        <is>
-          <t>https://conferences.i-cav.org/2027/</t>
-        </is>
-      </c>
+      <c r="K39" s="56" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
@@ -2901,57 +2905,57 @@
       <c r="K40" s="60" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>理论</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>LICS</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="39" t="inlineStr">
         <is>
           <t>ACM/IEEE Symposium on Logic in Computer Science</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="D41" s="40" t="inlineStr">
+        <is>
+          <t>Montréal, Canada</t>
+        </is>
+      </c>
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>06.21-06.24</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="inlineStr">
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>北美</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H41" s="42" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="I41" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/lics/</t>
         </is>
       </c>
-      <c r="J41" s="67" t="inlineStr">
+      <c r="J41" s="44" t="inlineStr">
         <is>
           <t>https://lics.siglog.org/lics27/</t>
         </is>
       </c>
-      <c r="K41" s="60" t="inlineStr"/>
+      <c r="K41" s="56" t="inlineStr"/>
     </row>
     <row r="42" ht="42.75" customHeight="1" s="37">
       <c r="A42" s="13" t="inlineStr">
@@ -3174,53 +3178,57 @@
       <c r="K45" s="60" t="inlineStr"/>
     </row>
     <row r="46" ht="27" customHeight="1" s="37">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>数据库</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>SIGIR</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="39" t="inlineStr">
         <is>
           <t>International ACM SIGIR Conference on Research and Development in Information Retrieval</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>San Jose, (California), USA</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="inlineStr">
+        <is>
+          <t>07.18-07.24</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>北美</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H46" s="42" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I46" s="46" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/sigir/</t>
         </is>
       </c>
-      <c r="J46" s="6" t="n"/>
-      <c r="K46" s="60" t="inlineStr"/>
+      <c r="J46" s="44" t="inlineStr">
+        <is>
+          <t>https://sigir2027.org/</t>
+        </is>
+      </c>
+      <c r="K46" s="56" t="inlineStr"/>
     </row>
     <row r="47" ht="28.5" customHeight="1" s="37">
       <c r="A47" s="13" t="inlineStr">
@@ -3333,57 +3341,57 @@
       <c r="K48" s="60" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="38" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>CVPR</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="39" t="inlineStr">
         <is>
           <t>IEEE/CVF Computer Vision and Pattern Recognition Conference</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="40" t="inlineStr">
         <is>
           <t>Seattle, WA, United States</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>06.20-06.24</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>06.20-06.25</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H49" s="42" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/cvpr/</t>
         </is>
       </c>
-      <c r="J49" s="67" t="inlineStr">
+      <c r="J49" s="44" t="inlineStr">
         <is>
           <t>https://cvpr.thecvf.com/Conferences/2027</t>
         </is>
       </c>
-      <c r="K49" s="60" t="inlineStr"/>
+      <c r="K49" s="56" t="inlineStr"/>
     </row>
     <row r="50" ht="28.5" customHeight="1" s="37">
       <c r="A50" s="38" t="inlineStr">
@@ -3403,7 +3411,7 @@
       </c>
       <c r="D50" s="40" t="inlineStr">
         <is>
-          <t>Hong Kong, CN October</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="E50" s="41" t="inlineStr">
@@ -3436,11 +3444,7 @@
           <t>https://iccv.thecvf.com/Conferences/2027</t>
         </is>
       </c>
-      <c r="K50" s="59" t="inlineStr">
-        <is>
-          <t>https://iccv.thecvf.com/Conferences/2025/CallForWorkshops</t>
-        </is>
-      </c>
+      <c r="K50" s="56" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
@@ -3496,53 +3500,57 @@
       <c r="K51" s="60" t="inlineStr"/>
     </row>
     <row r="52" ht="27" customHeight="1" s="37">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="38" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t>IJCAI</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="39" t="inlineStr">
         <is>
           <t>International Joint Conference on Artificial Intelligence</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
+      <c r="D52" s="40" t="inlineStr">
+        <is>
+          <t>Kyoto, Japan and Hengqin, China</t>
+        </is>
+      </c>
+      <c r="E52" s="41" t="inlineStr">
+        <is>
+          <t>08.15-08.17</t>
+        </is>
+      </c>
+      <c r="F52" s="40" t="inlineStr">
+        <is>
+          <t>亚太</t>
+        </is>
+      </c>
+      <c r="G52" s="40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H52" s="42" t="inlineStr">
         <is>
           <t>Morgan Kaufmann</t>
         </is>
       </c>
-      <c r="I52" s="17" t="inlineStr">
+      <c r="I52" s="43" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/ijcai/</t>
         </is>
       </c>
-      <c r="J52" s="6" t="n"/>
-      <c r="K52" s="60" t="inlineStr"/>
+      <c r="J52" s="44" t="inlineStr">
+        <is>
+          <t>https://www.ijcai.org/node/8</t>
+        </is>
+      </c>
+      <c r="K52" s="56" t="inlineStr"/>
     </row>
     <row r="53" ht="27" customHeight="1" s="37">
       <c r="A53" s="13" t="inlineStr">
@@ -3594,57 +3602,57 @@
       <c r="K53" s="60" t="inlineStr"/>
     </row>
     <row r="54" ht="42.75" customHeight="1" s="37">
-      <c r="A54" s="38" t="inlineStr">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>多媒体</t>
         </is>
       </c>
-      <c r="B54" s="38" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>SIGGRAPH</t>
         </is>
       </c>
-      <c r="C54" s="39" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>ACM Special Interest Group on Computer Graphics</t>
         </is>
       </c>
-      <c r="D54" s="40" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>Anaheim, (California), USA</t>
         </is>
       </c>
-      <c r="E54" s="41" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>08.08-08.12</t>
         </is>
       </c>
-      <c r="F54" s="40" t="inlineStr">
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G54" s="40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H54" s="42" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>ACM</t>
         </is>
       </c>
-      <c r="I54" s="43" t="inlineStr">
+      <c r="I54" s="17" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/siggraph/</t>
         </is>
       </c>
-      <c r="J54" s="44" t="inlineStr">
+      <c r="J54" s="67" t="inlineStr">
         <is>
           <t>https://s2027.siggraph.org/</t>
         </is>
       </c>
-      <c r="K54" s="56" t="inlineStr"/>
+      <c r="K54" s="60" t="inlineStr"/>
     </row>
     <row r="55" ht="28.5" customHeight="1" s="37">
       <c r="A55" s="13" t="inlineStr">
@@ -4121,57 +4129,57 @@
       <c r="K63" s="65" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="52" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="B64" s="52" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>MLsys</t>
         </is>
       </c>
-      <c r="C64" s="39" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Conference on Machine Learning and Systems</t>
         </is>
       </c>
-      <c r="D64" s="53" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Bellevue, (Washington), USA</t>
         </is>
       </c>
-      <c r="E64" s="53" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>06.21-06.25</t>
         </is>
       </c>
-      <c r="F64" s="53" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>北美</t>
         </is>
       </c>
-      <c r="G64" s="73" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H64" s="39" t="inlineStr">
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>MLSys/PMLR</t>
         </is>
       </c>
-      <c r="I64" s="46" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>https://mlsys.org/</t>
         </is>
       </c>
-      <c r="J64" s="44" t="inlineStr">
+      <c r="J64" s="67" t="inlineStr">
         <is>
           <t>https://mlsys.org/</t>
         </is>
       </c>
-      <c r="K64" s="63" t="inlineStr"/>
+      <c r="K64" s="65" t="inlineStr"/>
     </row>
     <row r="65" ht="29" customHeight="1" s="37">
       <c r="A65" s="52" t="inlineStr">
@@ -4192,7 +4200,7 @@
       </c>
       <c r="D65" s="53" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam Important Dates TPC Self-Nomination Deadline October</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="E65" s="53" t="inlineStr">
@@ -4673,7 +4681,7 @@
       </c>
       <c r="D74" s="40" t="inlineStr">
         <is>
-          <t>Athens, Greece. Venue</t>
+          <t>Athens, Greece</t>
         </is>
       </c>
       <c r="E74" s="40" t="inlineStr">
@@ -4701,7 +4709,7 @@
           <t>https://roboticsconference.org/</t>
         </is>
       </c>
-      <c r="J74" s="46" t="inlineStr">
+      <c r="J74" s="44" t="inlineStr">
         <is>
           <t>https://roboticsconference.org/</t>
         </is>
@@ -4868,57 +4876,57 @@
       <c r="K77" s="65" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="52" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>网络</t>
         </is>
       </c>
-      <c r="B78" s="52" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>WCNC</t>
         </is>
       </c>
-      <c r="C78" s="39" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>IEEE Wireless Communications and Networking Conference</t>
         </is>
       </c>
-      <c r="D78" s="53" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>Panama City, Panama</t>
         </is>
       </c>
-      <c r="E78" s="53" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>04.05-04.08</t>
         </is>
       </c>
-      <c r="F78" s="53" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>拉美</t>
         </is>
       </c>
-      <c r="G78" s="73" t="inlineStr">
+      <c r="G78" s="0" t="inlineStr">
         <is>
           <t>2026.10.05</t>
         </is>
       </c>
-      <c r="H78" s="39" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>IEEE</t>
         </is>
       </c>
-      <c r="I78" s="46" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>https://dblp.org/db/conf/wcnc/</t>
         </is>
       </c>
-      <c r="J78" s="44" t="inlineStr">
+      <c r="J78" s="67" t="inlineStr">
         <is>
           <t>https://wcnc2027.ieee-wcnc.org/</t>
         </is>
       </c>
-      <c r="K78" s="64" t="inlineStr">
+      <c r="K78" s="72" t="inlineStr">
         <is>
           <t>https://wcnc2027.ieee-wcnc.org/</t>
         </is>
@@ -5702,147 +5710,150 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId160"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.984251968503937" header="0.5118110236220472" footer="0.5118110236220472"/>
@@ -5864,7 +5875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9748,110 +9759,137 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="0" t="inlineStr">
         <is>
           <t>ASPLOS</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
         <is>
           <t>2026.11.04</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E156" s="0" t="inlineStr">
         <is>
           <t>2026-09-21 11:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="0" t="inlineStr">
         <is>
           <t>STOC</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D157" s="0" t="inlineStr">
         <is>
           <t>2027.04.01</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E157" s="0" t="inlineStr">
         <is>
           <t>2026-09-21 11:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="0" t="inlineStr">
         <is>
           <t>RSS</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="0" t="inlineStr">
         <is>
           <t>2026.04.23</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
+      <c r="D158" s="0" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E158" s="0" t="inlineStr">
         <is>
           <t>2026-09-21 11:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="0" t="inlineStr">
         <is>
           <t>WCNC</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="0" t="inlineStr">
         <is>
           <t>Workshop Submission Deadline（2027）</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C159" s="0" t="inlineStr">
         <is>
           <t>2026.10.01</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D159" s="0" t="inlineStr">
         <is>
           <t>2026.10.05</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E159" s="0" t="inlineStr">
         <is>
           <t>2026-09-21 11:17 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CAV</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Workshop Submission Deadline（2027）</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026.09.15</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:13 UTC</t>
         </is>
       </c>
     </row>
